--- a/site/Active-Directory-RingCentral-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-RingCentral-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,29 +551,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>RingCentral</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,32 +583,252 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
+          <t>h_01KRN274WCP66M2GN0KMH3CHVC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN274WCP66M2GN0KMH3CHVC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RingCentral Termination Settings</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KRN5PJH463G09Z993T1DQFGY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN5PJH463G09Z993T1DQFGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Notification Template Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KKTVPXVNCW5163JW89SS6E3B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVPXVNCW5163JW89SS6E3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Success Execution Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Failure Notification Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Skipped Records Notification Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KRN8DA5B6X0PP3WZPHC9Z897</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN8DA5B6X0PP3WZPHC9Z897</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KRN8509Z6VKEHBGKSXQX948K</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN8509Z6VKEHBGKSXQX948K</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>General Settings</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>h_01K421SEM89261VNA9S1Q7KWBV</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01K421SEM89261VNA9S1Q7KWBV</t>
         </is>

--- a/site/Active-Directory-RingCentral-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-RingCentral-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Features</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+          <t>h_01KRNKHJST2HAPXB7QZ9FFJB20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNKHJST2HAPXB7QZ9FFJB20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,41 +495,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01J46B7Y1FJFZ9EF69E21925AA</t>
+          <t>h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01J46B7Y1FJFZ9EF69E21925AA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01KRJZGDHVK39XCQKBKZFD5519</t>
+          <t>h_01J46B7Y1FJFZ9EF69E21925AA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRJZGDHVK39XCQKBKZFD5519</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01J46B7Y1FJFZ9EF69E21925AA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,19 +539,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01KRJZGDHVK39XCQKBKZFD5519</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRJZGDHVK39XCQKBKZFD5519</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,19 +561,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RingCentral</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,41 +583,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KRN274WCP66M2GN0KMH3CHVC</t>
+          <t>h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN274WCP66M2GN0KMH3CHVC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>RingCentral</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
+          <t>h_01KRN274WCP66M2GN0KMH3CHVC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN274WCP66M2GN0KMH3CHVC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RingCentral Termination Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,41 +627,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
+          <t>h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>RingCentral Termination Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KRN5PJH463G09Z993T1DQFGY</t>
+          <t>h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN5PJH463G09Z993T1DQFGY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,41 +671,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
+          <t>h_01KRN5PJH463G09Z993T1DQFGY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN5PJH463G09Z993T1DQFGY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KKTVPXVNCW5163JW89SS6E3B</t>
+          <t>h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVPXVNCW5163JW89SS6E3B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Success Execution Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
+          <t>h_01KKTVPXVNCW5163JW89SS6E3B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVPXVNCW5163JW89SS6E3B</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Failure Notification Settings</t>
+          <t>Success Execution Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
+          <t>h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Skipped Records Notification Settings</t>
+          <t>Failure Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KRN8DA5B6X0PP3WZPHC9Z897</t>
+          <t>h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN8DA5B6X0PP3WZPHC9Z897</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Skipped Records Notification Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,56 +781,276 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
+          <t>h_01KRNN2NSKY0Q5S07N7XVJAARV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNN2NSKY0Q5S07N7XVJAARV</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KRN8509Z6VKEHBGKSXQX948K</t>
+          <t>h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN8509Z6VKEHBGKSXQX948K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KRN8509Z6VKEHBGKSXQX948K</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN8509Z6VKEHBGKSXQX948K</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KRNC3HZERP4YP740KAT9E0MT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNC3HZERP4YP740KAT9E0MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>General Settings:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>h_01K421SEM89261VNA9S1Q7KWBV</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01K421SEM89261VNA9S1Q7KWBV</t>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KRNCA404J6PA0X55H2GX3RQ4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNCA404J6PA0X55H2GX3RQ4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KRNCVG8JJFBZ3ZHJ6KW24YKC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNCVG8JJFBZ3ZHJ6KW24YKC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Insights Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KRND0KS7FT66FNETBBE7WJ09</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRND0KS7FT66FNETBBE7WJ09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KRNDBHXB0C9YSKW7GP15ZE5P</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNDBHXB0C9YSKW7GP15ZE5P</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KRNDDEPKA5CVY5ADBK4DJQCA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNDDEPKA5CVY5ADBK4DJQCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Rollout Configuration</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KRNE64W4EJS88CQN398KKNE3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNE64W4EJS88CQN398KKNE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Limit Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KRNFEQFY16F9FQQBWFYPM43R</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNFEQFY16F9FQQBWFYPM43R</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PII Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KRNGRVY9MC0KJ8AS4TJC2784</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNGRVY9MC0KJ8AS4TJC2784</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>

--- a/site/Active-Directory-RingCentral-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-RingCentral-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,29 +551,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Integration Settings</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01KV7MB2ZF5PTJ2G3F9B777RED</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KV7MB2ZF5PTJ2G3F9B777RED</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,63 +583,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RingCentral</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KRN274WCP66M2GN0KMH3CHVC</t>
+          <t>h_01KV7G8PQSC1GREFYWHRN76JBC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN274WCP66M2GN0KMH3CHVC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KV7G8PQSC1GREFYWHRN76JBC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
+          <t>h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRK0BHV05EJ6TA89V11JBQ7H</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RingCentral Termination Settings</t>
+          <t>Active Directory Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
+          <t>h_01KV7DZQWR4G7K0KYZNWEWV8BV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KV7DZQWR4G7K0KYZNWEWV8BV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>RingCentral</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,129 +671,129 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KRN5PJH463G09Z993T1DQFGY</t>
+          <t>h_01KRN274WCP66M2GN0KMH3CHVC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN5PJH463G09Z993T1DQFGY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN274WCP66M2GN0KMH3CHVC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>RingCentral Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
+          <t>h_01KV7GRY9DSBZSX09RGK087F6T</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KV7GRY9DSBZSX09RGK087F6T</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KKTVPXVNCW5163JW89SS6E3B</t>
+          <t>h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVPXVNCW5163JW89SS6E3B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3TPHSBH2Y1D5NTQF9ZX8A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Success Execution Settings</t>
+          <t>RingCentral Termination Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
+          <t>h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN3SW89F5S7WTHFB2W0FY1C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Failure Notification Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
+          <t>h_01KRN5PJH463G09Z993T1DQFGY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN5PJH463G09Z993T1DQFGY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Skipped Records Notification Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KRNN2NSKY0Q5S07N7XVJAARV</t>
+          <t>h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNN2NSKY0Q5S07N7XVJAARV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN6FKTCRFBQ8HS2CBHNF816</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,63 +803,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
+          <t>h_01KKTVPXVNCW5163JW89SS6E3B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVPXVNCW5163JW89SS6E3B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KRN8509Z6VKEHBGKSXQX948K</t>
+          <t>h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN8509Z6VKEHBGKSXQX948K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6MCCGM52GCHN9HT70D</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KRNC3HZERP4YP740KAT9E0MT</t>
+          <t>h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNC3HZERP4YP740KAT9E0MT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6PB4FG3M60K73ZVPH8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>General Settings:</t>
+          <t>Skipping Execution</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KRNCA404J6PA0X55H2GX3RQ4</t>
+          <t>h_01KRNN2NSKY0Q5S07N7XVJAARV</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNCA404J6PA0X55H2GX3RQ4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNN2NSKY0Q5S07N7XVJAARV</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,85 +891,85 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KRNCVG8JJFBZ3ZHJ6KW24YKC</t>
+          <t>h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNCVG8JJFBZ3ZHJ6KW24YKC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KKTVMZ6R6GM9N0C0QYCB7HQ0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Insights Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KRND0KS7FT66FNETBBE7WJ09</t>
+          <t>h_01KRN8509Z6VKEHBGKSXQX948K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRND0KS7FT66FNETBBE7WJ09</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRN8509Z6VKEHBGKSXQX948K</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KRNDBHXB0C9YSKW7GP15ZE5P</t>
+          <t>h_01KRNC3HZERP4YP740KAT9E0MT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNDBHXB0C9YSKW7GP15ZE5P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNC3HZERP4YP740KAT9E0MT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>General Settings:</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KRNDDEPKA5CVY5ADBK4DJQCA</t>
+          <t>h_01KRNCA404J6PA0X55H2GX3RQ4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNDDEPKA5CVY5ADBK4DJQCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNCA404J6PA0X55H2GX3RQ4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rollout Configuration</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KRNE64W4EJS88CQN398KKNE3</t>
+          <t>h_01KRNCVG8JJFBZ3ZHJ6KW24YKC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNE64W4EJS88CQN398KKNE3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNCVG8JJFBZ3ZHJ6KW24YKC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Limit Settings</t>
+          <t>Insights Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,54 +1001,164 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KRNFEQFY16F9FQQBWFYPM43R</t>
+          <t>h_01KRND0KS7FT66FNETBBE7WJ09</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNFEQFY16F9FQQBWFYPM43R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRND0KS7FT66FNETBBE7WJ09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PII Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KRNGRVY9MC0KJ8AS4TJC2784</t>
+          <t>h_01KRNDBHXB0C9YSKW7GP15ZE5P</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNGRVY9MC0KJ8AS4TJC2784</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNDBHXB0C9YSKW7GP15ZE5P</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KRNDDEPKA5CVY5ADBK4DJQCA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNDDEPKA5CVY5ADBK4DJQCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Rollout Configuration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KRNE64W4EJS88CQN398KKNE3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNE64W4EJS88CQN398KKNE3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Debug Settings</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KV7JFVTK14T3YX3RMCBD1MZS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KV7JFVTK14T3YX3RMCBD1MZS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Limit Settings</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KRNFEQFY16F9FQQBWFYPM43R</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNFEQFY16F9FQQBWFYPM43R</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PII Settings</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KRNGRVY9MC0KJ8AS4TJC2784</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KRNGRVY9MC0KJ8AS4TJC2784</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>

--- a/site/Active-Directory-RingCentral-Integration-Guide/headings.xlsx
+++ b/site/Active-Directory-RingCentral-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,72 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Active-Directory-RingCentral-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
